--- a/Test Results/Excel/Passed_Test_Cases.xlsx
+++ b/Test Results/Excel/Passed_Test_Cases.xlsx
@@ -536,7 +536,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Execution Completed: 06 Oct 2026, 01:27 AM | Target Environment: Android App + Web Portal</t>
+          <t>Execution Completed: 06 Oct 2026, 01:40 AM | Target Environment: Android App + Web Portal</t>
         </is>
       </c>
     </row>
